--- a/Assets/Data/Dungeon0050.xlsx
+++ b/Assets/Data/Dungeon0050.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7960" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -52,16 +52,28 @@
     <t>■</t>
   </si>
   <si>
+    <t>Tr:D4</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Tr:D1</t>
+  </si>
+  <si>
+    <t>Ba</t>
+  </si>
+  <si>
     <t>Mv</t>
   </si>
   <si>
-    <t>Tr</t>
+    <t>Out</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>①</t>
   </si>
   <si>
-    <t>Out</t>
+    <t>Un</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -97,8 +109,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -117,24 +129,44 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -150,59 +182,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,7 +212,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,15 +258,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,13 +288,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,13 +354,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,7 +426,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,127 +462,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,6 +506,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -505,11 +532,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,8 +542,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,24 +565,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,145 +581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -730,12 +742,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -823,169 +835,193 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>7020</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>怨嗟床</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1322,16 +1358,16 @@
         <v>1</v>
       </c>
       <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
         <v>12</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>10</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1443,19 +1479,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -1464,19 +1500,23 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -1512,40 +1552,42 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -1581,38 +1623,40 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -1645,33 +1689,47 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -1704,39 +1762,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -1769,19 +1819,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1791,17 +1843,19 @@
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -1837,36 +1891,40 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -1902,19 +1960,27 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
         <v>9</v>
@@ -1922,8 +1988,12 @@
       <c r="M9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -1956,20 +2026,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
@@ -1981,6 +2057,14 @@
       <c r="M10" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="N10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10"/>
+      <c r="Q10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2010,25 +2094,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>8</v>
@@ -2043,6 +2123,14 @@
       <c r="M11" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11"/>
+      <c r="Q11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2072,22 +2160,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -2098,18 +2186,20 @@
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12"/>
       <c r="Q12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
@@ -2149,13 +2239,11 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -2166,15 +2254,21 @@
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
@@ -2204,18 +2298,50 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
@@ -2245,20 +2371,48 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -3451,19 +3605,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -3472,19 +3626,23 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -3520,40 +3678,44 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -3589,38 +3751,42 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -3653,33 +3819,47 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -3712,39 +3892,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -3777,19 +3949,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
@@ -3799,17 +3973,19 @@
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -3845,36 +4021,40 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -3910,19 +4090,27 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
         <v>9</v>
@@ -3930,8 +4118,12 @@
       <c r="M9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -3964,20 +4156,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
@@ -3987,6 +4185,12 @@
         <v>9</v>
       </c>
       <c r="M10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="S10" s="2"/>
@@ -4018,25 +4222,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>8</v>
@@ -4049,6 +4249,12 @@
         <v>9</v>
       </c>
       <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="S11" s="2"/>
@@ -4080,22 +4286,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -4106,17 +4312,19 @@
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="S12" s="2"/>
@@ -4157,13 +4365,11 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -4174,13 +4380,17 @@
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="R13" s="2"/>
@@ -4212,18 +4422,48 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
@@ -4253,20 +4493,48 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -5362,8 +5630,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="18.0909090909091" customWidth="1"/>
   </cols>
@@ -5373,34 +5641,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5411,7 +5679,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -5441,10 +5709,10 @@
         <v>50</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -5460,7 +5728,7 @@
         <v>51</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -5474,10 +5742,10 @@
         <v>50</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -5510,7 +5778,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3010</v>
@@ -5533,6 +5801,336 @@
       </c>
       <c r="K5" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3010</v>
+      </c>
+      <c r="F6">
+        <v>1010</v>
+      </c>
+      <c r="G6" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H6">
+        <v>1060</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>3010</v>
+      </c>
+      <c r="F7">
+        <v>1010</v>
+      </c>
+      <c r="G7" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H7">
+        <v>1070</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>3010</v>
+      </c>
+      <c r="F8">
+        <v>6010</v>
+      </c>
+      <c r="G8" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H8">
+        <v>124</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>3010</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
+        <v>なし</v>
+      </c>
+      <c r="H9">
+        <v>124</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>50</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3010</v>
+      </c>
+      <c r="F10">
+        <v>5010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>3010</v>
+      </c>
+      <c r="F11">
+        <v>1010</v>
+      </c>
+      <c r="G11" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H11">
+        <v>1070</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>3010</v>
+      </c>
+      <c r="F12">
+        <v>6010</v>
+      </c>
+      <c r="G12" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H12">
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>50</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>なし</v>
+      </c>
+      <c r="H13">
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>5010</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H14">
+        <v>-1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>8010</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Dungeon0050.xlsx
+++ b/Assets/Data/Dungeon0050.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -129,6 +129,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -143,8 +180,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,67 +220,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,6 +242,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -251,23 +267,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +288,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,19 +324,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,49 +360,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,61 +408,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,13 +438,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,36 +491,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -539,11 +509,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -565,11 +552,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -581,7 +581,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -590,13 +590,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -605,121 +605,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2063,7 +2063,6 @@
       <c r="O10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P10"/>
       <c r="Q10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
@@ -2129,7 +2128,6 @@
       <c r="O11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P11"/>
       <c r="Q11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
@@ -2199,7 +2197,6 @@
       <c r="O12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12"/>
       <c r="Q12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
@@ -5758,7 +5755,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>1100</v>
+        <v>4020</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5791,7 +5788,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H5">
-        <v>4020</v>
+        <v>5060</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/Assets/Data/Dungeon0050.xlsx
+++ b/Assets/Data/Dungeon0050.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -109,8 +109,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -129,9 +129,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,15 +167,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,20 +184,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,9 +205,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,7 +260,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,53 +268,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,7 +282,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,25 +342,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,49 +396,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,19 +420,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,55 +450,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,6 +494,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -503,8 +512,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,15 +559,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -581,145 +581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -799,9 +799,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -809,9 +807,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>

--- a/Assets/Data/Dungeon0050.xlsx
+++ b/Assets/Data/Dungeon0050.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -108,10 +108,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -136,60 +136,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -198,13 +144,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -220,8 +159,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -230,14 +176,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,24 +222,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -282,7 +282,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,7 +324,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,13 +348,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,109 +432,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,31 +456,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,26 +476,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,34 +499,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -573,6 +549,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -581,145 +581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0050.xlsx
+++ b/Assets/Data/Dungeon0050.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -58,7 +58,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>Tr:D1</t>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>Ba</t>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>①</t>
+  </si>
+  <si>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Un</t>
@@ -108,10 +111,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -136,8 +139,115 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -152,91 +262,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,30 +273,6 @@
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -282,7 +285,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,13 +393,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,19 +423,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,49 +447,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,79 +465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +479,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -505,32 +551,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,30 +576,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -581,145 +584,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3888,7 +3891,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
@@ -3905,7 +3908,7 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
@@ -4218,7 +4221,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
@@ -5634,34 +5637,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11">
